--- a/Reference.xlsx
+++ b/Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SMB\Common\EABI\Data Science\02_Projects and Working Files\42-SAID Calculator Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{52C4BA1A-3C2B-4F83-8AF7-9C393C0B89FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE2A529-DFC3-482D-B374-0D49DD328FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8750494C-CF25-47EB-BD97-9743966D7AE4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$670</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$672</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="18">
   <si>
     <t>Tier</t>
   </si>
@@ -512,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
-  <dimension ref="A1:G670"/>
+  <dimension ref="A1:G672"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="5" customWidth="1"/>
@@ -13194,7 +13194,7 @@
         <v>3</v>
       </c>
       <c r="E669" s="11">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
@@ -13208,14 +13208,48 @@
         <v>45322</v>
       </c>
       <c r="D670" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E670" s="11">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A671" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B671" s="6">
+        <v>45292</v>
+      </c>
+      <c r="C671" s="6">
+        <v>45322</v>
+      </c>
+      <c r="D671" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E671" s="11">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A672" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B672" s="6">
+        <v>45292</v>
+      </c>
+      <c r="C672" s="6">
+        <v>45322</v>
+      </c>
+      <c r="D672" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E672" s="11">
         <v>615</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E670" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}"/>
+  <autoFilter ref="A1:E672" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Reference.xlsx
+++ b/Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SMB\Common\EABI\Data Science\02_Projects and Working Files\42-SAID Calculator Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE2A529-DFC3-482D-B374-0D49DD328FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E50617-627E-4679-96EE-560ED038417A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8750494C-CF25-47EB-BD97-9743966D7AE4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$672</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$676</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="18">
   <si>
     <t>Tier</t>
   </si>
@@ -512,12 +512,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
-  <dimension ref="A1:G672"/>
+  <dimension ref="A1:G676"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" style="5" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="8" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" style="8" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="11"/>
   </cols>
@@ -10277,7 +10277,7 @@
         <v>45292</v>
       </c>
       <c r="C514" s="6">
-        <v>45322</v>
+        <v>45657</v>
       </c>
       <c r="D514" s="7" t="s">
         <v>3</v>
@@ -13001,7 +13001,7 @@
         <v>45292</v>
       </c>
       <c r="C658" s="6">
-        <v>45322</v>
+        <v>45657</v>
       </c>
       <c r="D658" s="7" t="s">
         <v>4</v>
@@ -13018,7 +13018,7 @@
         <v>45292</v>
       </c>
       <c r="C659" s="6">
-        <v>45322</v>
+        <v>45657</v>
       </c>
       <c r="D659" s="7" t="s">
         <v>4</v>
@@ -13035,7 +13035,7 @@
         <v>45292</v>
       </c>
       <c r="C660" s="6">
-        <v>45322</v>
+        <v>45657</v>
       </c>
       <c r="D660" s="7" t="s">
         <v>4</v>
@@ -13052,7 +13052,7 @@
         <v>45292</v>
       </c>
       <c r="C661" s="6">
-        <v>45322</v>
+        <v>45657</v>
       </c>
       <c r="D661" s="7" t="s">
         <v>4</v>
@@ -13248,8 +13248,76 @@
         <v>615</v>
       </c>
     </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A673" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B673" s="6">
+        <v>45292</v>
+      </c>
+      <c r="C673" s="6">
+        <v>45657</v>
+      </c>
+      <c r="D673" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E673" s="10">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A674" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B674" s="6">
+        <v>45292</v>
+      </c>
+      <c r="C674" s="6">
+        <v>45657</v>
+      </c>
+      <c r="D674" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E674" s="10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A675" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B675" s="6">
+        <v>45292</v>
+      </c>
+      <c r="C675" s="6">
+        <v>45657</v>
+      </c>
+      <c r="D675" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E675" s="10">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A676" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B676" s="6">
+        <v>45292</v>
+      </c>
+      <c r="C676" s="6">
+        <v>45657</v>
+      </c>
+      <c r="D676" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E676" s="10">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E672" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}"/>
+  <autoFilter ref="A1:E676" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Reference.xlsx
+++ b/Reference.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SMB\Common\EABI\Data Science\02_Projects and Working Files\42-SAID Calculator Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E50617-627E-4679-96EE-560ED038417A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FF07E9-524E-49F4-8C28-4356473A81E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8750494C-CF25-47EB-BD97-9743966D7AE4}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8750494C-CF25-47EB-BD97-9743966D7AE4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$676</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$679</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="18">
   <si>
     <t>Tier</t>
   </si>
@@ -512,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
-  <dimension ref="A1:G676"/>
+  <dimension ref="A1:G679"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="5" customWidth="1"/>
@@ -13316,8 +13316,59 @@
         <v>285</v>
       </c>
     </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A677" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B677" s="6">
+        <v>45323</v>
+      </c>
+      <c r="C677" s="6">
+        <v>45351</v>
+      </c>
+      <c r="D677" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E677" s="10">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A678" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B678" s="6">
+        <v>45323</v>
+      </c>
+      <c r="C678" s="6">
+        <v>45351</v>
+      </c>
+      <c r="D678" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E678" s="10">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A679" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B679" s="6">
+        <v>45323</v>
+      </c>
+      <c r="C679" s="6">
+        <v>45351</v>
+      </c>
+      <c r="D679" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E679" s="10">
+        <v>1118</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E676" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}"/>
+  <autoFilter ref="A1:E679" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Reference.xlsx
+++ b/Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SMB\Common\EABI\Data Science\02_Projects and Working Files\42-SAID Calculator Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FF07E9-524E-49F4-8C28-4356473A81E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4578F0-B1D3-4A03-ADC6-83AFBACFEA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8750494C-CF25-47EB-BD97-9743966D7AE4}"/>
   </bookViews>
@@ -512,6 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G679"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -541,7 +542,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -579,7 +580,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -598,7 +599,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -617,7 +618,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -655,7 +656,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
@@ -674,7 +675,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
@@ -693,7 +694,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>2</v>
       </c>
@@ -731,7 +732,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>2</v>
       </c>
@@ -750,7 +751,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
@@ -769,7 +770,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
@@ -807,7 +808,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>2</v>
       </c>
@@ -826,7 +827,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>2</v>
       </c>
@@ -845,7 +846,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>2</v>
       </c>
@@ -883,7 +884,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>2</v>
       </c>
@@ -902,7 +903,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>2</v>
       </c>
@@ -921,7 +922,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>2</v>
       </c>
@@ -959,7 +960,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>2</v>
       </c>
@@ -978,7 +979,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>2</v>
       </c>
@@ -997,7 +998,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>2</v>
       </c>
@@ -1035,7 +1036,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>2</v>
       </c>
@@ -1054,7 +1055,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>2</v>
       </c>
@@ -1073,7 +1074,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>2</v>
       </c>
@@ -1111,7 +1112,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
@@ -1130,7 +1131,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>2</v>
       </c>
@@ -1149,7 +1150,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>2</v>
       </c>
@@ -1187,7 +1188,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>2</v>
       </c>
@@ -1206,7 +1207,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>2</v>
       </c>
@@ -1225,7 +1226,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>2</v>
       </c>
@@ -1263,7 +1264,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>2</v>
       </c>
@@ -1282,7 +1283,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
@@ -1301,7 +1302,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>2</v>
       </c>
@@ -1339,7 +1340,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>2</v>
       </c>
@@ -1358,7 +1359,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>2</v>
       </c>
@@ -1377,7 +1378,7 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>2</v>
       </c>
@@ -1415,7 +1416,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>2</v>
       </c>
@@ -1434,7 +1435,7 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>2</v>
       </c>
@@ -1453,7 +1454,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
@@ -1491,7 +1492,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>2</v>
       </c>
@@ -1510,7 +1511,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>2</v>
       </c>
@@ -1529,7 +1530,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>2</v>
       </c>
@@ -1567,7 +1568,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>2</v>
       </c>
@@ -1586,7 +1587,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>2</v>
       </c>
@@ -1605,7 +1606,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>2</v>
       </c>
@@ -1643,7 +1644,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>2</v>
       </c>
@@ -1662,7 +1663,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>2</v>
       </c>
@@ -1681,7 +1682,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>2</v>
       </c>
@@ -1719,7 +1720,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>2</v>
       </c>
@@ -1738,7 +1739,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>2</v>
       </c>
@@ -1757,7 +1758,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>2</v>
       </c>
@@ -1795,7 +1796,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>2</v>
       </c>
@@ -1814,7 +1815,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>2</v>
       </c>
@@ -1833,7 +1834,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>2</v>
       </c>
@@ -1871,7 +1872,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>2</v>
       </c>
@@ -1890,7 +1891,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>2</v>
       </c>
@@ -1909,7 +1910,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>2</v>
       </c>
@@ -1947,7 +1948,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>2</v>
       </c>
@@ -1966,7 +1967,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>2</v>
       </c>
@@ -1985,7 +1986,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>2</v>
       </c>
@@ -2023,7 +2024,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>2</v>
       </c>
@@ -2042,7 +2043,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>2</v>
       </c>
@@ -2061,7 +2062,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>2</v>
       </c>
@@ -2099,7 +2100,7 @@
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>2</v>
       </c>
@@ -2118,7 +2119,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>2</v>
       </c>
@@ -2137,7 +2138,7 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>2</v>
       </c>
@@ -2175,7 +2176,7 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>2</v>
       </c>
@@ -2194,7 +2195,7 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>2</v>
       </c>
@@ -2213,7 +2214,7 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>2</v>
       </c>
@@ -2251,7 +2252,7 @@
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>2</v>
       </c>
@@ -2270,7 +2271,7 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>2</v>
       </c>
@@ -2289,7 +2290,7 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>2</v>
       </c>
@@ -2327,7 +2328,7 @@
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>2</v>
       </c>
@@ -2346,7 +2347,7 @@
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>2</v>
       </c>
@@ -2365,7 +2366,7 @@
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>2</v>
       </c>
@@ -2403,7 +2404,7 @@
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>2</v>
       </c>
@@ -2422,7 +2423,7 @@
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>2</v>
       </c>
@@ -2441,7 +2442,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>2</v>
       </c>
@@ -2479,7 +2480,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>2</v>
       </c>
@@ -2498,7 +2499,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>2</v>
       </c>
@@ -2517,7 +2518,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>2</v>
       </c>
@@ -2555,7 +2556,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>2</v>
       </c>
@@ -2574,7 +2575,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>2</v>
       </c>
@@ -2593,7 +2594,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>2</v>
       </c>
@@ -2631,7 +2632,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>2</v>
       </c>
@@ -2650,7 +2651,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>2</v>
       </c>
@@ -2669,7 +2670,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>2</v>
       </c>
@@ -2707,7 +2708,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>2</v>
       </c>
@@ -2726,7 +2727,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>2</v>
       </c>
@@ -2745,7 +2746,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>2</v>
       </c>
@@ -2783,7 +2784,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>2</v>
       </c>
@@ -2802,7 +2803,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>2</v>
       </c>
@@ -2821,7 +2822,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>2</v>
       </c>
@@ -2859,7 +2860,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>2</v>
       </c>
@@ -2878,7 +2879,7 @@
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>2</v>
       </c>
@@ -2897,7 +2898,7 @@
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>2</v>
       </c>
@@ -2935,7 +2936,7 @@
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>2</v>
       </c>
@@ -2954,7 +2955,7 @@
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>2</v>
       </c>
@@ -2973,7 +2974,7 @@
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>2</v>
       </c>
@@ -3011,7 +3012,7 @@
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>2</v>
       </c>
@@ -3030,7 +3031,7 @@
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>2</v>
       </c>
@@ -3049,7 +3050,7 @@
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>2</v>
       </c>
@@ -3087,7 +3088,7 @@
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>2</v>
       </c>
@@ -3106,7 +3107,7 @@
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>2</v>
       </c>
@@ -3125,7 +3126,7 @@
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>2</v>
       </c>
@@ -3163,7 +3164,7 @@
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>2</v>
       </c>
@@ -3182,7 +3183,7 @@
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>2</v>
       </c>
@@ -3201,7 +3202,7 @@
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>2</v>
       </c>
@@ -3239,7 +3240,7 @@
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>2</v>
       </c>
@@ -3258,7 +3259,7 @@
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>2</v>
       </c>
@@ -3277,7 +3278,7 @@
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>2</v>
       </c>
@@ -3315,7 +3316,7 @@
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>2</v>
       </c>
@@ -3334,7 +3335,7 @@
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>2</v>
       </c>
@@ -3353,7 +3354,7 @@
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>2</v>
       </c>
@@ -3391,7 +3392,7 @@
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>2</v>
       </c>
@@ -3410,7 +3411,7 @@
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>2</v>
       </c>
@@ -3429,7 +3430,7 @@
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>2</v>
       </c>
@@ -3467,7 +3468,7 @@
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>2</v>
       </c>
@@ -3486,7 +3487,7 @@
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>2</v>
       </c>
@@ -3505,7 +3506,7 @@
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>2</v>
       </c>
@@ -3543,7 +3544,7 @@
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>2</v>
       </c>
@@ -3562,7 +3563,7 @@
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>2</v>
       </c>
@@ -3581,7 +3582,7 @@
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>2</v>
       </c>
@@ -3619,7 +3620,7 @@
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>2</v>
       </c>
@@ -3638,7 +3639,7 @@
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>2</v>
       </c>
@@ -3657,7 +3658,7 @@
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>2</v>
       </c>
@@ -3695,7 +3696,7 @@
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>2</v>
       </c>
@@ -3714,7 +3715,7 @@
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>2</v>
       </c>
@@ -3733,7 +3734,7 @@
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>2</v>
       </c>
@@ -3771,7 +3772,7 @@
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>2</v>
       </c>
@@ -3790,7 +3791,7 @@
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>2</v>
       </c>
@@ -3809,7 +3810,7 @@
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>2</v>
       </c>
@@ -3847,7 +3848,7 @@
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>2</v>
       </c>
@@ -3866,7 +3867,7 @@
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>2</v>
       </c>
@@ -3885,7 +3886,7 @@
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>2</v>
       </c>
@@ -3923,7 +3924,7 @@
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>2</v>
       </c>
@@ -3942,7 +3943,7 @@
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>2</v>
       </c>
@@ -3961,7 +3962,7 @@
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>2</v>
       </c>
@@ -3999,7 +4000,7 @@
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>2</v>
       </c>
@@ -4018,7 +4019,7 @@
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>2</v>
       </c>
@@ -4037,7 +4038,7 @@
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>2</v>
       </c>
@@ -4075,7 +4076,7 @@
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>2</v>
       </c>
@@ -4094,7 +4095,7 @@
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>2</v>
       </c>
@@ -4113,7 +4114,7 @@
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>2</v>
       </c>
@@ -4151,7 +4152,7 @@
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>2</v>
       </c>
@@ -4170,7 +4171,7 @@
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>2</v>
       </c>
@@ -4189,7 +4190,7 @@
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>2</v>
       </c>
@@ -4227,7 +4228,7 @@
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>2</v>
       </c>
@@ -4246,7 +4247,7 @@
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>2</v>
       </c>
@@ -4265,7 +4266,7 @@
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>2</v>
       </c>
@@ -4303,7 +4304,7 @@
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>2</v>
       </c>
@@ -4322,7 +4323,7 @@
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>2</v>
       </c>
@@ -4341,7 +4342,7 @@
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>2</v>
       </c>
@@ -4379,7 +4380,7 @@
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>2</v>
       </c>
@@ -4398,7 +4399,7 @@
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>2</v>
       </c>
@@ -4417,7 +4418,7 @@
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>2</v>
       </c>
@@ -4455,7 +4456,7 @@
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>2</v>
       </c>
@@ -4474,7 +4475,7 @@
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>2</v>
       </c>
@@ -4493,7 +4494,7 @@
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>2</v>
       </c>
@@ -4531,7 +4532,7 @@
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>2</v>
       </c>
@@ -4550,7 +4551,7 @@
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>2</v>
       </c>
@@ -4569,7 +4570,7 @@
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>2</v>
       </c>
@@ -4607,7 +4608,7 @@
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>2</v>
       </c>
@@ -4626,7 +4627,7 @@
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>2</v>
       </c>
@@ -4645,7 +4646,7 @@
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>2</v>
       </c>
@@ -4683,7 +4684,7 @@
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>2</v>
       </c>
@@ -4702,7 +4703,7 @@
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>2</v>
       </c>
@@ -4721,7 +4722,7 @@
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>2</v>
       </c>
@@ -4759,7 +4760,7 @@
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>2</v>
       </c>
@@ -4778,7 +4779,7 @@
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>2</v>
       </c>
@@ -4797,7 +4798,7 @@
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>2</v>
       </c>
@@ -4835,7 +4836,7 @@
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>2</v>
       </c>
@@ -4854,7 +4855,7 @@
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>2</v>
       </c>
@@ -4873,7 +4874,7 @@
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>2</v>
       </c>
@@ -4911,7 +4912,7 @@
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>2</v>
       </c>
@@ -4930,7 +4931,7 @@
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>2</v>
       </c>
@@ -4949,7 +4950,7 @@
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>2</v>
       </c>
@@ -4987,7 +4988,7 @@
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>2</v>
       </c>
@@ -5006,7 +5007,7 @@
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>2</v>
       </c>
@@ -5025,7 +5026,7 @@
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>2</v>
       </c>
@@ -5063,7 +5064,7 @@
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>2</v>
       </c>
@@ -5082,7 +5083,7 @@
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>2</v>
       </c>
@@ -5101,7 +5102,7 @@
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>2</v>
       </c>
@@ -5139,7 +5140,7 @@
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>2</v>
       </c>
@@ -5158,7 +5159,7 @@
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>2</v>
       </c>
@@ -5177,7 +5178,7 @@
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>2</v>
       </c>
@@ -5215,7 +5216,7 @@
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>2</v>
       </c>
@@ -5234,7 +5235,7 @@
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>2</v>
       </c>
@@ -5253,7 +5254,7 @@
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>2</v>
       </c>
@@ -5291,7 +5292,7 @@
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>2</v>
       </c>
@@ -5310,7 +5311,7 @@
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>2</v>
       </c>
@@ -5329,7 +5330,7 @@
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>2</v>
       </c>
@@ -5367,7 +5368,7 @@
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>2</v>
       </c>
@@ -5386,7 +5387,7 @@
       <c r="F256" s="1"/>
       <c r="G256" s="1"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>2</v>
       </c>
@@ -5405,7 +5406,7 @@
       <c r="F257" s="1"/>
       <c r="G257" s="1"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>2</v>
       </c>
@@ -5443,7 +5444,7 @@
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>2</v>
       </c>
@@ -5462,7 +5463,7 @@
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>2</v>
       </c>
@@ -5481,7 +5482,7 @@
       <c r="F261" s="1"/>
       <c r="G261" s="1"/>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
         <v>2</v>
       </c>
@@ -5519,7 +5520,7 @@
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
         <v>2</v>
       </c>
@@ -5538,7 +5539,7 @@
       <c r="F264" s="1"/>
       <c r="G264" s="1"/>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
         <v>2</v>
       </c>
@@ -5557,7 +5558,7 @@
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
         <v>2</v>
       </c>
@@ -5595,7 +5596,7 @@
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
         <v>2</v>
       </c>
@@ -5614,7 +5615,7 @@
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
         <v>2</v>
       </c>
@@ -5633,7 +5634,7 @@
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
         <v>2</v>
       </c>
@@ -5671,7 +5672,7 @@
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
         <v>2</v>
       </c>
@@ -5690,7 +5691,7 @@
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
         <v>2</v>
       </c>
@@ -5709,7 +5710,7 @@
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
         <v>2</v>
       </c>
@@ -5747,7 +5748,7 @@
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
         <v>2</v>
       </c>
@@ -5766,7 +5767,7 @@
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>2</v>
       </c>
@@ -5785,7 +5786,7 @@
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>2</v>
       </c>
@@ -5823,7 +5824,7 @@
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>2</v>
       </c>
@@ -5842,7 +5843,7 @@
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>2</v>
       </c>
@@ -5861,7 +5862,7 @@
       <c r="F281" s="1"/>
       <c r="G281" s="1"/>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>2</v>
       </c>
@@ -5899,7 +5900,7 @@
       <c r="F283" s="1"/>
       <c r="G283" s="1"/>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>2</v>
       </c>
@@ -5918,7 +5919,7 @@
       <c r="F284" s="1"/>
       <c r="G284" s="1"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>2</v>
       </c>
@@ -5937,7 +5938,7 @@
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
         <v>2</v>
       </c>
@@ -5975,7 +5976,7 @@
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
         <v>2</v>
       </c>
@@ -5994,7 +5995,7 @@
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
         <v>2</v>
       </c>
@@ -6013,7 +6014,7 @@
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
         <v>2</v>
       </c>
@@ -6051,7 +6052,7 @@
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
         <v>2</v>
       </c>
@@ -6070,7 +6071,7 @@
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
         <v>2</v>
       </c>
@@ -6089,7 +6090,7 @@
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
         <v>2</v>
       </c>
@@ -6127,7 +6128,7 @@
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
         <v>2</v>
       </c>
@@ -6146,7 +6147,7 @@
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
         <v>2</v>
       </c>
@@ -6165,7 +6166,7 @@
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
         <v>2</v>
       </c>
@@ -6203,7 +6204,7 @@
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
         <v>2</v>
       </c>
@@ -6222,7 +6223,7 @@
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
         <v>2</v>
       </c>
@@ -6241,7 +6242,7 @@
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
         <v>2</v>
       </c>
@@ -6279,7 +6280,7 @@
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
         <v>2</v>
       </c>
@@ -6298,7 +6299,7 @@
       <c r="F304" s="1"/>
       <c r="G304" s="1"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
         <v>2</v>
       </c>
@@ -6317,7 +6318,7 @@
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
         <v>2</v>
       </c>
@@ -6355,7 +6356,7 @@
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
         <v>2</v>
       </c>
@@ -6374,7 +6375,7 @@
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
         <v>2</v>
       </c>
@@ -6393,7 +6394,7 @@
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
         <v>2</v>
       </c>
@@ -6431,7 +6432,7 @@
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
         <v>2</v>
       </c>
@@ -6450,7 +6451,7 @@
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
         <v>2</v>
       </c>
@@ -6469,7 +6470,7 @@
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
         <v>2</v>
       </c>
@@ -6507,7 +6508,7 @@
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>2</v>
       </c>
@@ -6526,7 +6527,7 @@
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
         <v>2</v>
       </c>
@@ -6545,7 +6546,7 @@
       <c r="F317" s="1"/>
       <c r="G317" s="1"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>2</v>
       </c>
@@ -6583,7 +6584,7 @@
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
         <v>2</v>
       </c>
@@ -6602,7 +6603,7 @@
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
         <v>2</v>
       </c>
@@ -6621,7 +6622,7 @@
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
         <v>2</v>
       </c>
@@ -6659,7 +6660,7 @@
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
         <v>2</v>
       </c>
@@ -6678,7 +6679,7 @@
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
         <v>2</v>
       </c>
@@ -6697,7 +6698,7 @@
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
         <v>2</v>
       </c>
@@ -6735,7 +6736,7 @@
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
         <v>2</v>
       </c>
@@ -6754,7 +6755,7 @@
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
         <v>2</v>
       </c>
@@ -6773,7 +6774,7 @@
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
         <v>2</v>
       </c>
@@ -6811,7 +6812,7 @@
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
         <v>2</v>
       </c>
@@ -6830,7 +6831,7 @@
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
         <v>2</v>
       </c>
@@ -6849,7 +6850,7 @@
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
         <v>2</v>
       </c>
@@ -6887,7 +6888,7 @@
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
         <v>2</v>
       </c>
@@ -6906,7 +6907,7 @@
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
         <v>2</v>
       </c>
@@ -6925,7 +6926,7 @@
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
         <v>2</v>
       </c>
@@ -6963,7 +6964,7 @@
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
         <v>2</v>
       </c>
@@ -6982,7 +6983,7 @@
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
         <v>2</v>
       </c>
@@ -7001,7 +7002,7 @@
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
         <v>2</v>
       </c>
@@ -7039,7 +7040,7 @@
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
         <v>2</v>
       </c>
@@ -7058,7 +7059,7 @@
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
         <v>2</v>
       </c>
@@ -7077,7 +7078,7 @@
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
         <v>2</v>
       </c>
@@ -7115,7 +7116,7 @@
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
         <v>2</v>
       </c>
@@ -7134,7 +7135,7 @@
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
         <v>2</v>
       </c>
@@ -7153,7 +7154,7 @@
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
         <v>2</v>
       </c>
@@ -7191,7 +7192,7 @@
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
         <v>2</v>
       </c>
@@ -7210,7 +7211,7 @@
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
         <v>2</v>
       </c>
@@ -7229,7 +7230,7 @@
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
         <v>2</v>
       </c>
@@ -7267,7 +7268,7 @@
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
         <v>2</v>
       </c>
@@ -7286,7 +7287,7 @@
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
         <v>2</v>
       </c>
@@ -7305,7 +7306,7 @@
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
         <v>2</v>
       </c>
@@ -7343,7 +7344,7 @@
       <c r="F359" s="1"/>
       <c r="G359" s="1"/>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>2</v>
       </c>
@@ -7362,7 +7363,7 @@
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>2</v>
       </c>
@@ -7381,7 +7382,7 @@
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
         <v>2</v>
       </c>
@@ -7419,7 +7420,7 @@
       <c r="F363" s="1"/>
       <c r="G363" s="1"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
         <v>2</v>
       </c>
@@ -7438,7 +7439,7 @@
       <c r="F364" s="1"/>
       <c r="G364" s="1"/>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
         <v>2</v>
       </c>
@@ -7457,7 +7458,7 @@
       <c r="F365" s="1"/>
       <c r="G365" s="1"/>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
         <v>2</v>
       </c>
@@ -7495,7 +7496,7 @@
       <c r="F367" s="1"/>
       <c r="G367" s="1"/>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
         <v>2</v>
       </c>
@@ -7514,7 +7515,7 @@
       <c r="F368" s="1"/>
       <c r="G368" s="1"/>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
         <v>2</v>
       </c>
@@ -7533,7 +7534,7 @@
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
         <v>2</v>
       </c>
@@ -7571,7 +7572,7 @@
       <c r="F371" s="1"/>
       <c r="G371" s="1"/>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
         <v>2</v>
       </c>
@@ -7590,7 +7591,7 @@
       <c r="F372" s="1"/>
       <c r="G372" s="1"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
         <v>2</v>
       </c>
@@ -7609,7 +7610,7 @@
       <c r="F373" s="1"/>
       <c r="G373" s="1"/>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
         <v>2</v>
       </c>
@@ -7647,7 +7648,7 @@
       <c r="F375" s="1"/>
       <c r="G375" s="1"/>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
         <v>2</v>
       </c>
@@ -7666,7 +7667,7 @@
       <c r="F376" s="1"/>
       <c r="G376" s="1"/>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
         <v>2</v>
       </c>
@@ -7685,7 +7686,7 @@
       <c r="F377" s="1"/>
       <c r="G377" s="1"/>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
         <v>2</v>
       </c>
@@ -7723,7 +7724,7 @@
       <c r="F379" s="1"/>
       <c r="G379" s="1"/>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
         <v>2</v>
       </c>
@@ -7742,7 +7743,7 @@
       <c r="F380" s="1"/>
       <c r="G380" s="1"/>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
         <v>2</v>
       </c>
@@ -7761,7 +7762,7 @@
       <c r="F381" s="1"/>
       <c r="G381" s="1"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
         <v>2</v>
       </c>
@@ -7799,7 +7800,7 @@
       <c r="F383" s="1"/>
       <c r="G383" s="1"/>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
         <v>2</v>
       </c>
@@ -7818,7 +7819,7 @@
       <c r="F384" s="1"/>
       <c r="G384" s="1"/>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
         <v>2</v>
       </c>
@@ -7837,7 +7838,7 @@
       <c r="F385" s="1"/>
       <c r="G385" s="1"/>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
         <v>2</v>
       </c>
@@ -7875,7 +7876,7 @@
       <c r="F387" s="1"/>
       <c r="G387" s="1"/>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
         <v>2</v>
       </c>
@@ -7894,7 +7895,7 @@
       <c r="F388" s="1"/>
       <c r="G388" s="1"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
         <v>2</v>
       </c>
@@ -7913,7 +7914,7 @@
       <c r="F389" s="1"/>
       <c r="G389" s="1"/>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
         <v>2</v>
       </c>
@@ -7951,7 +7952,7 @@
       <c r="F391" s="1"/>
       <c r="G391" s="1"/>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
         <v>2</v>
       </c>
@@ -7970,7 +7971,7 @@
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
         <v>2</v>
       </c>
@@ -7989,7 +7990,7 @@
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
         <v>2</v>
       </c>
@@ -8027,7 +8028,7 @@
       <c r="F395" s="1"/>
       <c r="G395" s="1"/>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
         <v>2</v>
       </c>
@@ -8046,7 +8047,7 @@
       <c r="F396" s="1"/>
       <c r="G396" s="1"/>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
         <v>2</v>
       </c>
@@ -8065,7 +8066,7 @@
       <c r="F397" s="1"/>
       <c r="G397" s="1"/>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
         <v>2</v>
       </c>
@@ -8103,7 +8104,7 @@
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
         <v>2</v>
       </c>
@@ -8122,7 +8123,7 @@
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
         <v>2</v>
       </c>
@@ -8141,7 +8142,7 @@
       <c r="F401" s="1"/>
       <c r="G401" s="1"/>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
         <v>2</v>
       </c>
@@ -8179,7 +8180,7 @@
       <c r="F403" s="1"/>
       <c r="G403" s="1"/>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
         <v>2</v>
       </c>
@@ -8198,7 +8199,7 @@
       <c r="F404" s="1"/>
       <c r="G404" s="1"/>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
         <v>2</v>
       </c>
@@ -8217,7 +8218,7 @@
       <c r="F405" s="1"/>
       <c r="G405" s="1"/>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
         <v>2</v>
       </c>
@@ -8255,7 +8256,7 @@
       <c r="F407" s="1"/>
       <c r="G407" s="1"/>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
         <v>2</v>
       </c>
@@ -8274,7 +8275,7 @@
       <c r="F408" s="1"/>
       <c r="G408" s="1"/>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
         <v>2</v>
       </c>
@@ -8293,7 +8294,7 @@
       <c r="F409" s="1"/>
       <c r="G409" s="1"/>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
         <v>2</v>
       </c>
@@ -8331,7 +8332,7 @@
       <c r="F411" s="1"/>
       <c r="G411" s="1"/>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
         <v>2</v>
       </c>
@@ -8350,7 +8351,7 @@
       <c r="F412" s="1"/>
       <c r="G412" s="1"/>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
         <v>2</v>
       </c>
@@ -8369,7 +8370,7 @@
       <c r="F413" s="1"/>
       <c r="G413" s="1"/>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
         <v>2</v>
       </c>
@@ -8407,7 +8408,7 @@
       <c r="F415" s="1"/>
       <c r="G415" s="1"/>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
         <v>2</v>
       </c>
@@ -8426,7 +8427,7 @@
       <c r="F416" s="1"/>
       <c r="G416" s="1"/>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
         <v>2</v>
       </c>
@@ -8445,7 +8446,7 @@
       <c r="F417" s="1"/>
       <c r="G417" s="1"/>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
         <v>2</v>
       </c>
@@ -8483,7 +8484,7 @@
       <c r="F419" s="1"/>
       <c r="G419" s="1"/>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
         <v>2</v>
       </c>
@@ -8502,7 +8503,7 @@
       <c r="F420" s="1"/>
       <c r="G420" s="1"/>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
         <v>2</v>
       </c>
@@ -8521,7 +8522,7 @@
       <c r="F421" s="1"/>
       <c r="G421" s="1"/>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
         <v>2</v>
       </c>
@@ -8559,7 +8560,7 @@
       <c r="F423" s="1"/>
       <c r="G423" s="1"/>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
         <v>2</v>
       </c>
@@ -8578,7 +8579,7 @@
       <c r="F424" s="1"/>
       <c r="G424" s="1"/>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
         <v>2</v>
       </c>
@@ -8597,7 +8598,7 @@
       <c r="F425" s="1"/>
       <c r="G425" s="1"/>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
         <v>2</v>
       </c>
@@ -8635,7 +8636,7 @@
       <c r="F427" s="1"/>
       <c r="G427" s="1"/>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
         <v>2</v>
       </c>
@@ -8654,7 +8655,7 @@
       <c r="F428" s="1"/>
       <c r="G428" s="1"/>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
         <v>2</v>
       </c>
@@ -8673,7 +8674,7 @@
       <c r="F429" s="1"/>
       <c r="G429" s="1"/>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
         <v>2</v>
       </c>
@@ -8711,7 +8712,7 @@
       <c r="F431" s="1"/>
       <c r="G431" s="1"/>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
         <v>2</v>
       </c>
@@ -8730,7 +8731,7 @@
       <c r="F432" s="1"/>
       <c r="G432" s="1"/>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
         <v>2</v>
       </c>
@@ -8749,7 +8750,7 @@
       <c r="F433" s="1"/>
       <c r="G433" s="1"/>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
         <v>2</v>
       </c>
@@ -8787,7 +8788,7 @@
       <c r="F435" s="1"/>
       <c r="G435" s="1"/>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
         <v>2</v>
       </c>
@@ -8806,7 +8807,7 @@
       <c r="F436" s="1"/>
       <c r="G436" s="1"/>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
         <v>2</v>
       </c>
@@ -8825,7 +8826,7 @@
       <c r="F437" s="1"/>
       <c r="G437" s="1"/>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
         <v>2</v>
       </c>
@@ -8863,7 +8864,7 @@
       <c r="F439" s="1"/>
       <c r="G439" s="1"/>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
         <v>2</v>
       </c>
@@ -8882,7 +8883,7 @@
       <c r="F440" s="1"/>
       <c r="G440" s="1"/>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
         <v>2</v>
       </c>
@@ -8901,7 +8902,7 @@
       <c r="F441" s="1"/>
       <c r="G441" s="1"/>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
         <v>2</v>
       </c>
@@ -8939,7 +8940,7 @@
       <c r="F443" s="1"/>
       <c r="G443" s="1"/>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
         <v>2</v>
       </c>
@@ -8958,7 +8959,7 @@
       <c r="F444" s="1"/>
       <c r="G444" s="1"/>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
         <v>2</v>
       </c>
@@ -8977,7 +8978,7 @@
       <c r="F445" s="1"/>
       <c r="G445" s="1"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
         <v>2</v>
       </c>
@@ -9015,7 +9016,7 @@
       <c r="F447" s="1"/>
       <c r="G447" s="1"/>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
         <v>2</v>
       </c>
@@ -9034,7 +9035,7 @@
       <c r="F448" s="1"/>
       <c r="G448" s="1"/>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
         <v>2</v>
       </c>
@@ -9053,7 +9054,7 @@
       <c r="F449" s="1"/>
       <c r="G449" s="1"/>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
         <v>2</v>
       </c>
@@ -9091,7 +9092,7 @@
       <c r="F451" s="1"/>
       <c r="G451" s="1"/>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
         <v>2</v>
       </c>
@@ -9110,7 +9111,7 @@
       <c r="F452" s="1"/>
       <c r="G452" s="1"/>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
         <v>2</v>
       </c>
@@ -9129,7 +9130,7 @@
       <c r="F453" s="1"/>
       <c r="G453" s="1"/>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
         <v>2</v>
       </c>
@@ -9167,7 +9168,7 @@
       <c r="F455" s="1"/>
       <c r="G455" s="1"/>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
         <v>2</v>
       </c>
@@ -9186,7 +9187,7 @@
       <c r="F456" s="1"/>
       <c r="G456" s="1"/>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
         <v>2</v>
       </c>
@@ -9205,7 +9206,7 @@
       <c r="F457" s="1"/>
       <c r="G457" s="1"/>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="4" t="s">
         <v>2</v>
       </c>
@@ -9243,7 +9244,7 @@
       <c r="F459" s="1"/>
       <c r="G459" s="1"/>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="4" t="s">
         <v>2</v>
       </c>
@@ -9262,7 +9263,7 @@
       <c r="F460" s="1"/>
       <c r="G460" s="1"/>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="4" t="s">
         <v>2</v>
       </c>
@@ -9281,7 +9282,7 @@
       <c r="F461" s="1"/>
       <c r="G461" s="1"/>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="4" t="s">
         <v>2</v>
       </c>
@@ -9319,7 +9320,7 @@
       <c r="F463" s="1"/>
       <c r="G463" s="1"/>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="4" t="s">
         <v>2</v>
       </c>
@@ -9338,7 +9339,7 @@
       <c r="F464" s="1"/>
       <c r="G464" s="1"/>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="4" t="s">
         <v>2</v>
       </c>
@@ -9357,7 +9358,7 @@
       <c r="F465" s="1"/>
       <c r="G465" s="1"/>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="4" t="s">
         <v>2</v>
       </c>
@@ -9395,7 +9396,7 @@
       <c r="F467" s="1"/>
       <c r="G467" s="1"/>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="4" t="s">
         <v>2</v>
       </c>
@@ -9414,7 +9415,7 @@
       <c r="F468" s="1"/>
       <c r="G468" s="1"/>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="4" t="s">
         <v>2</v>
       </c>
@@ -9433,7 +9434,7 @@
       <c r="F469" s="1"/>
       <c r="G469" s="1"/>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="4" t="s">
         <v>2</v>
       </c>
@@ -9471,7 +9472,7 @@
       <c r="F471" s="1"/>
       <c r="G471" s="1"/>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="4" t="s">
         <v>2</v>
       </c>
@@ -9490,7 +9491,7 @@
       <c r="F472" s="1"/>
       <c r="G472" s="1"/>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="4" t="s">
         <v>2</v>
       </c>
@@ -9509,7 +9510,7 @@
       <c r="F473" s="1"/>
       <c r="G473" s="1"/>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="4" t="s">
         <v>2</v>
       </c>
@@ -9547,7 +9548,7 @@
       <c r="F475" s="1"/>
       <c r="G475" s="1"/>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="4" t="s">
         <v>2</v>
       </c>
@@ -9566,7 +9567,7 @@
       <c r="F476" s="1"/>
       <c r="G476" s="1"/>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="4" t="s">
         <v>2</v>
       </c>
@@ -9585,7 +9586,7 @@
       <c r="F477" s="1"/>
       <c r="G477" s="1"/>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="4" t="s">
         <v>2</v>
       </c>
@@ -9623,7 +9624,7 @@
       <c r="F479" s="1"/>
       <c r="G479" s="1"/>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="4" t="s">
         <v>2</v>
       </c>
@@ -9642,7 +9643,7 @@
       <c r="F480" s="1"/>
       <c r="G480" s="1"/>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="4" t="s">
         <v>2</v>
       </c>
@@ -9661,7 +9662,7 @@
       <c r="F481" s="1"/>
       <c r="G481" s="1"/>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="4" t="s">
         <v>2</v>
       </c>
@@ -9699,7 +9700,7 @@
       <c r="F483" s="1"/>
       <c r="G483" s="1"/>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="4" t="s">
         <v>2</v>
       </c>
@@ -9718,7 +9719,7 @@
       <c r="F484" s="1"/>
       <c r="G484" s="1"/>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="4" t="s">
         <v>2</v>
       </c>
@@ -9737,7 +9738,7 @@
       <c r="F485" s="1"/>
       <c r="G485" s="1"/>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="4" t="s">
         <v>2</v>
       </c>
@@ -9775,7 +9776,7 @@
       <c r="F487" s="1"/>
       <c r="G487" s="1"/>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="4" t="s">
         <v>2</v>
       </c>
@@ -9794,7 +9795,7 @@
       <c r="F488" s="1"/>
       <c r="G488" s="1"/>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="4" t="s">
         <v>2</v>
       </c>
@@ -9813,7 +9814,7 @@
       <c r="F489" s="1"/>
       <c r="G489" s="1"/>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="4" t="s">
         <v>2</v>
       </c>
@@ -9851,7 +9852,7 @@
       <c r="F491" s="1"/>
       <c r="G491" s="1"/>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="4" t="s">
         <v>2</v>
       </c>
@@ -9870,7 +9871,7 @@
       <c r="F492" s="1"/>
       <c r="G492" s="1"/>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="4" t="s">
         <v>2</v>
       </c>
@@ -9889,7 +9890,7 @@
       <c r="F493" s="1"/>
       <c r="G493" s="1"/>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="4" t="s">
         <v>2</v>
       </c>
@@ -9927,7 +9928,7 @@
       <c r="F495" s="1"/>
       <c r="G495" s="1"/>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="4" t="s">
         <v>2</v>
       </c>
@@ -9946,7 +9947,7 @@
       <c r="F496" s="1"/>
       <c r="G496" s="1"/>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="4" t="s">
         <v>2</v>
       </c>
@@ -9965,7 +9966,7 @@
       <c r="F497" s="1"/>
       <c r="G497" s="1"/>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="4" t="s">
         <v>2</v>
       </c>
@@ -10003,7 +10004,7 @@
       <c r="F499" s="1"/>
       <c r="G499" s="1"/>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
         <v>2</v>
       </c>
@@ -10022,7 +10023,7 @@
       <c r="F500" s="1"/>
       <c r="G500" s="1"/>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="4" t="s">
         <v>2</v>
       </c>
@@ -10041,7 +10042,7 @@
       <c r="F501" s="1"/>
       <c r="G501" s="1"/>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="4" t="s">
         <v>2</v>
       </c>
@@ -10079,7 +10080,7 @@
       <c r="F503" s="1"/>
       <c r="G503" s="1"/>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="4" t="s">
         <v>2</v>
       </c>
@@ -10098,7 +10099,7 @@
       <c r="F504" s="1"/>
       <c r="G504" s="1"/>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="4" t="s">
         <v>2</v>
       </c>
@@ -10117,7 +10118,7 @@
       <c r="F505" s="1"/>
       <c r="G505" s="1"/>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="4" t="s">
         <v>2</v>
       </c>
@@ -10155,7 +10156,7 @@
       <c r="F507" s="1"/>
       <c r="G507" s="1"/>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="4" t="s">
         <v>2</v>
       </c>
@@ -10174,7 +10175,7 @@
       <c r="F508" s="1"/>
       <c r="G508" s="1"/>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="4" t="s">
         <v>2</v>
       </c>
@@ -10193,7 +10194,7 @@
       <c r="F509" s="1"/>
       <c r="G509" s="1"/>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="4" t="s">
         <v>2</v>
       </c>
@@ -10231,7 +10232,7 @@
       <c r="F511" s="1"/>
       <c r="G511" s="1"/>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="4" t="s">
         <v>2</v>
       </c>
@@ -10250,7 +10251,7 @@
       <c r="F512" s="1"/>
       <c r="G512" s="1"/>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="4" t="s">
         <v>2</v>
       </c>
@@ -10269,7 +10270,7 @@
       <c r="F513" s="1"/>
       <c r="G513" s="1"/>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="4" t="s">
         <v>7</v>
       </c>
@@ -10288,7 +10289,7 @@
       <c r="F514" s="1"/>
       <c r="G514" s="1"/>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="4" t="s">
         <v>8</v>
       </c>
@@ -10307,7 +10308,7 @@
       <c r="F515" s="1"/>
       <c r="G515" s="1"/>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="4" t="s">
         <v>9</v>
       </c>
@@ -10326,7 +10327,7 @@
       <c r="F516" s="1"/>
       <c r="G516" s="1"/>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="4" t="s">
         <v>10</v>
       </c>
@@ -10345,7 +10346,7 @@
       <c r="F517" s="1"/>
       <c r="G517" s="1"/>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="4" t="s">
         <v>11</v>
       </c>
@@ -10364,7 +10365,7 @@
       <c r="F518" s="1"/>
       <c r="G518" s="1"/>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="4" t="s">
         <v>7</v>
       </c>
@@ -10383,7 +10384,7 @@
       <c r="F519" s="1"/>
       <c r="G519" s="1"/>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="4" t="s">
         <v>8</v>
       </c>
@@ -10402,7 +10403,7 @@
       <c r="F520" s="1"/>
       <c r="G520" s="1"/>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="4" t="s">
         <v>9</v>
       </c>
@@ -10421,7 +10422,7 @@
       <c r="F521" s="1"/>
       <c r="G521" s="1"/>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="4" t="s">
         <v>10</v>
       </c>
@@ -10440,7 +10441,7 @@
       <c r="F522" s="1"/>
       <c r="G522" s="1"/>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="4" t="s">
         <v>11</v>
       </c>
@@ -10459,7 +10460,7 @@
       <c r="F523" s="1"/>
       <c r="G523" s="1"/>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="4" t="s">
         <v>7</v>
       </c>
@@ -10478,7 +10479,7 @@
       <c r="F524" s="1"/>
       <c r="G524" s="1"/>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="4" t="s">
         <v>8</v>
       </c>
@@ -10497,7 +10498,7 @@
       <c r="F525" s="1"/>
       <c r="G525" s="1"/>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="4" t="s">
         <v>9</v>
       </c>
@@ -10516,7 +10517,7 @@
       <c r="F526" s="1"/>
       <c r="G526" s="1"/>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="4" t="s">
         <v>10</v>
       </c>
@@ -10535,7 +10536,7 @@
       <c r="F527" s="1"/>
       <c r="G527" s="1"/>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="4" t="s">
         <v>11</v>
       </c>
@@ -10554,7 +10555,7 @@
       <c r="F528" s="1"/>
       <c r="G528" s="1"/>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="4" t="s">
         <v>7</v>
       </c>
@@ -10573,7 +10574,7 @@
       <c r="F529" s="1"/>
       <c r="G529" s="1"/>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="4" t="s">
         <v>8</v>
       </c>
@@ -10592,7 +10593,7 @@
       <c r="F530" s="1"/>
       <c r="G530" s="1"/>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="4" t="s">
         <v>9</v>
       </c>
@@ -10630,7 +10631,7 @@
       <c r="F532" s="1"/>
       <c r="G532" s="1"/>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="4" t="s">
         <v>11</v>
       </c>
@@ -10725,7 +10726,7 @@
       <c r="F537" s="1"/>
       <c r="G537" s="1"/>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="4" t="s">
         <v>11</v>
       </c>
@@ -10744,7 +10745,7 @@
       <c r="F538" s="1"/>
       <c r="G538" s="1"/>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="4" t="s">
         <v>7</v>
       </c>
@@ -10820,7 +10821,7 @@
       <c r="F542" s="1"/>
       <c r="G542" s="1"/>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="4" t="s">
         <v>11</v>
       </c>
@@ -10839,7 +10840,7 @@
       <c r="F543" s="1"/>
       <c r="G543" s="1"/>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="4" t="s">
         <v>7</v>
       </c>
@@ -10915,7 +10916,7 @@
       <c r="F547" s="1"/>
       <c r="G547" s="1"/>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="4" t="s">
         <v>11</v>
       </c>
@@ -10991,7 +10992,7 @@
       <c r="F551" s="1"/>
       <c r="G551" s="1"/>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="4" t="s">
         <v>11</v>
       </c>
@@ -11067,7 +11068,7 @@
       <c r="F555" s="1"/>
       <c r="G555" s="1"/>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="4" t="s">
         <v>11</v>
       </c>
@@ -11143,7 +11144,7 @@
       <c r="F559" s="1"/>
       <c r="G559" s="1"/>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="4" t="s">
         <v>11</v>
       </c>
@@ -11219,7 +11220,7 @@
       <c r="F563" s="1"/>
       <c r="G563" s="1"/>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="4" t="s">
         <v>11</v>
       </c>
@@ -11295,7 +11296,7 @@
       <c r="F567" s="1"/>
       <c r="G567" s="1"/>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="4" t="s">
         <v>11</v>
       </c>
@@ -11352,7 +11353,7 @@
       <c r="F570" s="1"/>
       <c r="G570" s="1"/>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="4" t="s">
         <v>10</v>
       </c>
@@ -11371,7 +11372,7 @@
       <c r="F571" s="1"/>
       <c r="G571" s="1"/>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="4" t="s">
         <v>12</v>
       </c>
@@ -11390,7 +11391,7 @@
       <c r="F572" s="1"/>
       <c r="G572" s="1"/>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="4" t="s">
         <v>11</v>
       </c>
@@ -11409,7 +11410,7 @@
       <c r="F573" s="1"/>
       <c r="G573" s="1"/>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="4" t="s">
         <v>8</v>
       </c>
@@ -11428,7 +11429,7 @@
       <c r="F574" s="1"/>
       <c r="G574" s="1"/>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="4" t="s">
         <v>9</v>
       </c>
@@ -11485,7 +11486,7 @@
       <c r="F577" s="1"/>
       <c r="G577" s="1"/>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="4" t="s">
         <v>11</v>
       </c>
@@ -11504,7 +11505,7 @@
       <c r="F578" s="1"/>
       <c r="G578" s="1"/>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="4" t="s">
         <v>8</v>
       </c>
@@ -11523,7 +11524,7 @@
       <c r="F579" s="1"/>
       <c r="G579" s="1"/>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="4" t="s">
         <v>9</v>
       </c>
@@ -11542,7 +11543,7 @@
       <c r="F580" s="1"/>
       <c r="G580" s="1"/>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="4" t="s">
         <v>10</v>
       </c>
@@ -11561,7 +11562,7 @@
       <c r="F581" s="1"/>
       <c r="G581" s="1"/>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="4" t="s">
         <v>12</v>
       </c>
@@ -11580,7 +11581,7 @@
       <c r="F582" s="1"/>
       <c r="G582" s="1"/>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="4" t="s">
         <v>11</v>
       </c>
@@ -11599,7 +11600,7 @@
       <c r="F583" s="1"/>
       <c r="G583" s="1"/>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="4" t="s">
         <v>8</v>
       </c>
@@ -11618,7 +11619,7 @@
       <c r="F584" s="1"/>
       <c r="G584" s="1"/>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="4" t="s">
         <v>9</v>
       </c>
@@ -11637,7 +11638,7 @@
       <c r="F585" s="1"/>
       <c r="G585" s="1"/>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="4" t="s">
         <v>10</v>
       </c>
@@ -11656,7 +11657,7 @@
       <c r="F586" s="1"/>
       <c r="G586" s="1"/>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="4" t="s">
         <v>12</v>
       </c>
@@ -11675,7 +11676,7 @@
       <c r="F587" s="1"/>
       <c r="G587" s="1"/>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="4" t="s">
         <v>11</v>
       </c>
@@ -11694,7 +11695,7 @@
       <c r="F588" s="1"/>
       <c r="G588" s="1"/>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="4" t="s">
         <v>8</v>
       </c>
@@ -11713,7 +11714,7 @@
       <c r="F589" s="1"/>
       <c r="G589" s="1"/>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="4" t="s">
         <v>9</v>
       </c>
@@ -11751,7 +11752,7 @@
       <c r="F591" s="1"/>
       <c r="G591" s="1"/>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="4" t="s">
         <v>11</v>
       </c>
@@ -11770,7 +11771,7 @@
       <c r="F592" s="1"/>
       <c r="G592" s="1"/>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="4" t="s">
         <v>8</v>
       </c>
@@ -11789,7 +11790,7 @@
       <c r="F593" s="1"/>
       <c r="G593" s="1"/>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="4" t="s">
         <v>9</v>
       </c>
@@ -11827,7 +11828,7 @@
       <c r="F595" s="1"/>
       <c r="G595" s="1"/>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="4" t="s">
         <v>11</v>
       </c>
@@ -11846,7 +11847,7 @@
       <c r="F596" s="1"/>
       <c r="G596" s="1"/>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="4" t="s">
         <v>8</v>
       </c>
@@ -11865,7 +11866,7 @@
       <c r="F597" s="1"/>
       <c r="G597" s="1"/>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="4" t="s">
         <v>9</v>
       </c>
@@ -11884,7 +11885,7 @@
       <c r="F598" s="1"/>
       <c r="G598" s="1"/>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="4" t="s">
         <v>11</v>
       </c>
@@ -11903,7 +11904,7 @@
       <c r="F599" s="1"/>
       <c r="G599" s="1"/>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="4" t="s">
         <v>8</v>
       </c>
@@ -11922,7 +11923,7 @@
       <c r="F600" s="1"/>
       <c r="G600" s="1"/>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="4" t="s">
         <v>9</v>
       </c>
@@ -11941,7 +11942,7 @@
       <c r="F601" s="1"/>
       <c r="G601" s="1"/>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="4" t="s">
         <v>11</v>
       </c>
@@ -11960,7 +11961,7 @@
       <c r="F602" s="1"/>
       <c r="G602" s="1"/>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="4" t="s">
         <v>8</v>
       </c>
@@ -11979,7 +11980,7 @@
       <c r="F603" s="1"/>
       <c r="G603" s="1"/>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="4" t="s">
         <v>9</v>
       </c>
@@ -11998,7 +11999,7 @@
       <c r="F604" s="1"/>
       <c r="G604" s="1"/>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="4" t="s">
         <v>11</v>
       </c>
@@ -12017,7 +12018,7 @@
       <c r="F605" s="1"/>
       <c r="G605" s="1"/>
     </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="4" t="s">
         <v>8</v>
       </c>
@@ -12036,7 +12037,7 @@
       <c r="F606" s="1"/>
       <c r="G606" s="1"/>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="4" t="s">
         <v>9</v>
       </c>
@@ -12074,7 +12075,7 @@
       <c r="F608" s="1"/>
       <c r="G608" s="1"/>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="4" t="s">
         <v>8</v>
       </c>
@@ -12093,7 +12094,7 @@
       <c r="F609" s="1"/>
       <c r="G609" s="1"/>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="4" t="s">
         <v>9</v>
       </c>
@@ -12131,7 +12132,7 @@
       <c r="F611" s="1"/>
       <c r="G611" s="1"/>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="4" t="s">
         <v>8</v>
       </c>
@@ -12150,7 +12151,7 @@
       <c r="F612" s="1"/>
       <c r="G612" s="1"/>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="4" t="s">
         <v>9</v>
       </c>
@@ -12188,7 +12189,7 @@
       <c r="F614" s="1"/>
       <c r="G614" s="1"/>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="4" t="s">
         <v>8</v>
       </c>
@@ -12245,7 +12246,7 @@
       <c r="F617" s="1"/>
       <c r="G617" s="1"/>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="4" t="s">
         <v>12</v>
       </c>
@@ -12264,7 +12265,7 @@
       <c r="F618" s="1"/>
       <c r="G618" s="1"/>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="4" t="s">
         <v>11</v>
       </c>
@@ -12283,7 +12284,7 @@
       <c r="F619" s="1"/>
       <c r="G619" s="1"/>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="4" t="s">
         <v>8</v>
       </c>
@@ -12302,7 +12303,7 @@
       <c r="F620" s="1"/>
       <c r="G620" s="1"/>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="4" t="s">
         <v>9</v>
       </c>
@@ -12340,7 +12341,7 @@
       <c r="F622" s="1"/>
       <c r="G622" s="1"/>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="4" t="s">
         <v>12</v>
       </c>
@@ -12359,7 +12360,7 @@
       <c r="F623" s="1"/>
       <c r="G623" s="1"/>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="4" t="s">
         <v>8</v>
       </c>
@@ -12378,7 +12379,7 @@
       <c r="F624" s="1"/>
       <c r="G624" s="1"/>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="4" t="s">
         <v>9</v>
       </c>
@@ -12416,7 +12417,7 @@
       <c r="F626" s="1"/>
       <c r="G626" s="1"/>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="4" t="s">
         <v>12</v>
       </c>
@@ -12435,7 +12436,7 @@
       <c r="F627" s="1"/>
       <c r="G627" s="1"/>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="4" t="s">
         <v>8</v>
       </c>
@@ -12454,7 +12455,7 @@
       <c r="F628" s="1"/>
       <c r="G628" s="1"/>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="4" t="s">
         <v>10</v>
       </c>
@@ -12473,7 +12474,7 @@
       <c r="F629" s="1"/>
       <c r="G629" s="1"/>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="4" t="s">
         <v>12</v>
       </c>
@@ -12492,7 +12493,7 @@
       <c r="F630" s="1"/>
       <c r="G630" s="1"/>
     </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="4" t="s">
         <v>8</v>
       </c>
@@ -12511,7 +12512,7 @@
       <c r="F631" s="1"/>
       <c r="G631" s="1"/>
     </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="4" t="s">
         <v>10</v>
       </c>
@@ -12530,7 +12531,7 @@
       <c r="F632" s="1"/>
       <c r="G632" s="1"/>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="4" t="s">
         <v>12</v>
       </c>
@@ -12549,7 +12550,7 @@
       <c r="F633" s="1"/>
       <c r="G633" s="1"/>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="4" t="s">
         <v>8</v>
       </c>
@@ -12568,7 +12569,7 @@
       <c r="F634" s="1"/>
       <c r="G634" s="1"/>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="4" t="s">
         <v>10</v>
       </c>
@@ -12587,7 +12588,7 @@
       <c r="F635" s="1"/>
       <c r="G635" s="1"/>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="4" t="s">
         <v>12</v>
       </c>
@@ -12606,7 +12607,7 @@
       <c r="F636" s="1"/>
       <c r="G636" s="1"/>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="4" t="s">
         <v>8</v>
       </c>
@@ -12625,7 +12626,7 @@
       <c r="F637" s="1"/>
       <c r="G637" s="1"/>
     </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="4" t="s">
         <v>12</v>
       </c>
@@ -12644,7 +12645,7 @@
       <c r="F638" s="1"/>
       <c r="G638" s="1"/>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="4" t="s">
         <v>8</v>
       </c>
@@ -12663,7 +12664,7 @@
       <c r="F639" s="1"/>
       <c r="G639" s="1"/>
     </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="4" t="s">
         <v>12</v>
       </c>
@@ -12682,7 +12683,7 @@
       <c r="F640" s="1"/>
       <c r="G640" s="1"/>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="4" t="s">
         <v>8</v>
       </c>
@@ -12701,7 +12702,7 @@
       <c r="F641" s="1"/>
       <c r="G641" s="1"/>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="4" t="s">
         <v>12</v>
       </c>
@@ -12720,7 +12721,7 @@
       <c r="F642" s="1"/>
       <c r="G642" s="1"/>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="4" t="s">
         <v>8</v>
       </c>
@@ -12739,7 +12740,7 @@
       <c r="F643" s="1"/>
       <c r="G643" s="1"/>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="4" t="s">
         <v>12</v>
       </c>
@@ -12758,7 +12759,7 @@
       <c r="F644" s="1"/>
       <c r="G644" s="1"/>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="4" t="s">
         <v>8</v>
       </c>
@@ -12777,7 +12778,7 @@
       <c r="F645" s="1"/>
       <c r="G645" s="1"/>
     </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="4" t="s">
         <v>12</v>
       </c>
@@ -12796,7 +12797,7 @@
       <c r="F646" s="1"/>
       <c r="G646" s="1"/>
     </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="4" t="s">
         <v>8</v>
       </c>
@@ -12815,7 +12816,7 @@
       <c r="F647" s="1"/>
       <c r="G647" s="1"/>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="4" t="s">
         <v>12</v>
       </c>
@@ -12853,7 +12854,7 @@
       <c r="F649" s="1"/>
       <c r="G649" s="1"/>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="4" t="s">
         <v>11</v>
       </c>
@@ -12872,7 +12873,7 @@
       <c r="F650" s="1"/>
       <c r="G650" s="1"/>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="4" t="s">
         <v>11</v>
       </c>
@@ -12891,7 +12892,7 @@
       <c r="F651" s="1"/>
       <c r="G651" s="1"/>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="5" t="s">
         <v>2</v>
       </c>
@@ -12908,7 +12909,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="5" t="s">
         <v>16</v>
       </c>
@@ -12925,7 +12926,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>17</v>
       </c>
@@ -12959,7 +12960,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>17</v>
       </c>
@@ -12976,7 +12977,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>17</v>
       </c>
@@ -13066,10 +13067,10 @@
         <v>12</v>
       </c>
       <c r="B662" s="6">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="C662" s="6">
-        <v>45351</v>
+        <v>45657</v>
       </c>
       <c r="D662" s="7" t="s">
         <v>4</v>
@@ -13078,7 +13079,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="4" t="s">
         <v>12</v>
       </c>
@@ -13095,7 +13096,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="4" t="s">
         <v>12</v>
       </c>
@@ -13117,10 +13118,10 @@
         <v>12</v>
       </c>
       <c r="B665" s="6">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="C665" s="6">
-        <v>45351</v>
+        <v>45657</v>
       </c>
       <c r="D665" s="7" t="s">
         <v>4</v>
@@ -13134,10 +13135,10 @@
         <v>12</v>
       </c>
       <c r="B666" s="6">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="C666" s="6">
-        <v>45351</v>
+        <v>45657</v>
       </c>
       <c r="D666" s="7" t="s">
         <v>4</v>
@@ -13151,10 +13152,10 @@
         <v>12</v>
       </c>
       <c r="B667" s="6">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="C667" s="6">
-        <v>45351</v>
+        <v>45657</v>
       </c>
       <c r="D667" s="7" t="s">
         <v>4</v>
@@ -13163,7 +13164,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="5" t="s">
         <v>2</v>
       </c>
@@ -13180,7 +13181,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="5" t="s">
         <v>2</v>
       </c>
@@ -13231,7 +13232,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="5" t="s">
         <v>2</v>
       </c>
@@ -13248,7 +13249,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="4" t="s">
         <v>7</v>
       </c>
@@ -13265,7 +13266,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="4" t="s">
         <v>7</v>
       </c>
@@ -13282,7 +13283,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="4" t="s">
         <v>7</v>
       </c>
@@ -13299,7 +13300,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="4" t="s">
         <v>7</v>
       </c>
@@ -13316,7 +13317,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="4" t="s">
         <v>12</v>
       </c>
@@ -13333,7 +13334,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="4" t="s">
         <v>12</v>
       </c>
@@ -13350,7 +13351,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="4" t="s">
         <v>12</v>
       </c>
@@ -13368,7 +13369,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E679" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}"/>
+  <autoFilter ref="A1:E679" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="B"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Reference.xlsx
+++ b/Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SMB\Common\EABI\Data Science\02_Projects and Working Files\42-SAID Calculator Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4578F0-B1D3-4A03-ADC6-83AFBACFEA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7636BC2E-9BD8-4E89-9DC8-26A970BB7EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8750494C-CF25-47EB-BD97-9743966D7AE4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$679</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$683</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="18">
   <si>
     <t>Tier</t>
   </si>
@@ -513,7 +513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G679"/>
+  <dimension ref="A1:G683"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="5" customWidth="1"/>
@@ -13368,8 +13368,76 @@
         <v>1118</v>
       </c>
     </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A680" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B680" s="6">
+        <v>44927</v>
+      </c>
+      <c r="C680" s="6">
+        <v>45291</v>
+      </c>
+      <c r="D680" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E680" s="10">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A681" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B681" s="6">
+        <v>44927</v>
+      </c>
+      <c r="C681" s="6">
+        <v>45291</v>
+      </c>
+      <c r="D681" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E681" s="10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A682" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B682" s="6">
+        <v>44927</v>
+      </c>
+      <c r="C682" s="6">
+        <v>45291</v>
+      </c>
+      <c r="D682" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E682" s="10">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A683" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B683" s="6">
+        <v>44927</v>
+      </c>
+      <c r="C683" s="6">
+        <v>45291</v>
+      </c>
+      <c r="D683" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E683" s="10">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E679" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
+  <autoFilter ref="A1:E683" xr:uid="{0F1448D5-A723-44B1-88DF-230A1B1FBE53}">
     <filterColumn colId="3">
       <filters>
         <filter val="B"/>
